--- a/upload/obitos-2025.xlsx
+++ b/upload/obitos-2025.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="21">
   <si>
     <t>unidade</t>
   </si>
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1086"/>
+  <dimension ref="A1:E1100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -18110,19 +18110,19 @@
     </row>
     <row r="1042" spans="1:5">
       <c r="A1042" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B1042" s="2">
         <v>2026</v>
       </c>
       <c r="C1042" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D1042" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1042" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1043" spans="1:5">
@@ -18133,47 +18133,47 @@
         <v>2026</v>
       </c>
       <c r="C1043" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1043" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1043" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1044" spans="1:5">
       <c r="A1044" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1044" s="2">
         <v>2026</v>
       </c>
       <c r="C1044" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D1044" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E1044" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1045" spans="1:5">
       <c r="A1045" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1045" s="2">
         <v>2026</v>
       </c>
       <c r="C1045" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1045" s="3">
         <v>2</v>
       </c>
       <c r="E1045" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1046" spans="1:5">
@@ -18184,13 +18184,13 @@
         <v>2026</v>
       </c>
       <c r="C1046" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D1046" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1046" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1047" spans="1:5">
@@ -18201,64 +18201,64 @@
         <v>2026</v>
       </c>
       <c r="C1047" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D1047" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E1047" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1048" spans="1:5">
       <c r="A1048" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1048" s="2">
         <v>2026</v>
       </c>
       <c r="C1048" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D1048" s="3">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E1048" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1049" spans="1:5">
       <c r="A1049" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1049" s="2">
         <v>2026</v>
       </c>
       <c r="C1049" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1049" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E1049" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1050" spans="1:5">
       <c r="A1050" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1050" s="2">
         <v>2026</v>
       </c>
       <c r="C1050" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D1050" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E1050" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1051" spans="1:5">
@@ -18269,86 +18269,86 @@
         <v>2026</v>
       </c>
       <c r="C1051" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D1051" s="3">
+        <v>27</v>
+      </c>
+      <c r="E1051" s="3">
         <v>25</v>
-      </c>
-      <c r="E1051" s="3">
-        <v>24</v>
       </c>
     </row>
     <row r="1052" spans="1:5">
       <c r="A1052" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1052" s="2">
         <v>2026</v>
       </c>
       <c r="C1052" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1052" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E1052" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1053" spans="1:5">
       <c r="A1053" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1053" s="2">
         <v>2026</v>
       </c>
       <c r="C1053" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1053" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E1053" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1054" spans="1:5">
       <c r="A1054" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1054" s="2">
         <v>2026</v>
       </c>
       <c r="C1054" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1054" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E1054" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1055" spans="1:5">
       <c r="A1055" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1055" s="2">
         <v>2026</v>
       </c>
       <c r="C1055" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1055" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E1055" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1056" spans="1:5">
       <c r="A1056" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1056" s="2">
         <v>2026</v>
@@ -18357,15 +18357,15 @@
         <v>1</v>
       </c>
       <c r="D1056" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E1056" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1057" spans="1:5">
       <c r="A1057" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1057" s="2">
         <v>2026</v>
@@ -18374,15 +18374,15 @@
         <v>2</v>
       </c>
       <c r="D1057" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E1057" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1058" spans="1:5">
       <c r="A1058" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1058" s="2">
         <v>2026</v>
@@ -18391,15 +18391,15 @@
         <v>3</v>
       </c>
       <c r="D1058" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E1058" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1059" spans="1:5">
       <c r="A1059" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1059" s="2">
         <v>2026</v>
@@ -18408,270 +18408,270 @@
         <v>4</v>
       </c>
       <c r="D1059" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E1059" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1060" spans="1:5">
       <c r="A1060" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1060" s="2">
         <v>2026</v>
       </c>
       <c r="C1060" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D1060" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1060" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1061" spans="1:5">
       <c r="A1061" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1061" s="2">
         <v>2026</v>
       </c>
       <c r="C1061" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1061" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E1061" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1062" spans="1:5">
       <c r="A1062" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1062" s="2">
         <v>2026</v>
       </c>
       <c r="C1062" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D1062" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1062" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1063" spans="1:5">
       <c r="A1063" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B1063" s="2">
         <v>2026</v>
       </c>
       <c r="C1063" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D1063" s="3">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E1063" s="3">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1064" spans="1:5">
       <c r="A1064" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B1064" s="2">
         <v>2026</v>
       </c>
       <c r="C1064" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1064" s="3">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="E1064" s="3">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1065" spans="1:5">
       <c r="A1065" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B1065" s="2">
         <v>2026</v>
       </c>
       <c r="C1065" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D1065" s="3">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="E1065" s="3">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1066" spans="1:5">
       <c r="A1066" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1066" s="2">
         <v>2026</v>
       </c>
       <c r="C1066" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D1066" s="3">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="E1066" s="3">
-        <v>59</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1067" spans="1:5">
       <c r="A1067" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1067" s="2">
         <v>2026</v>
       </c>
       <c r="C1067" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1067" s="3">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E1067" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1068" spans="1:5">
       <c r="A1068" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1068" s="2">
         <v>2026</v>
       </c>
       <c r="C1068" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1068" s="3">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="E1068" s="3">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1069" spans="1:5">
       <c r="A1069" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1069" s="2">
         <v>2026</v>
       </c>
       <c r="C1069" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D1069" s="3">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="E1069" s="3">
-        <v>38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1070" spans="1:5">
       <c r="A1070" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1070" s="2">
         <v>2026</v>
       </c>
       <c r="C1070" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D1070" s="3">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E1070" s="3">
-        <v>35</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1071" spans="1:5">
       <c r="A1071" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1071" s="2">
         <v>2026</v>
       </c>
       <c r="C1071" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1071" s="3">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="E1071" s="3">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1072" spans="1:5">
       <c r="A1072" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1072" s="2">
         <v>2026</v>
       </c>
       <c r="C1072" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1072" s="3">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="E1072" s="3">
-        <v>26</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1073" spans="1:5">
       <c r="A1073" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1073" s="2">
         <v>2026</v>
       </c>
       <c r="C1073" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1073" s="3">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="E1073" s="3">
-        <v>18</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1074" spans="1:5">
       <c r="A1074" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1074" s="2">
         <v>2026</v>
       </c>
       <c r="C1074" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1074" s="3">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="E1074" s="3">
-        <v>29</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1075" spans="1:5">
       <c r="A1075" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B1075" s="2">
         <v>2026</v>
@@ -18680,15 +18680,15 @@
         <v>1</v>
       </c>
       <c r="D1075" s="3">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E1075" s="3">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1076" spans="1:5">
       <c r="A1076" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B1076" s="2">
         <v>2026</v>
@@ -18697,15 +18697,15 @@
         <v>2</v>
       </c>
       <c r="D1076" s="3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E1076" s="3">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1077" spans="1:5">
       <c r="A1077" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B1077" s="2">
         <v>2026</v>
@@ -18714,15 +18714,15 @@
         <v>3</v>
       </c>
       <c r="D1077" s="3">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E1077" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1078" spans="1:5">
       <c r="A1078" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B1078" s="2">
         <v>2026</v>
@@ -18731,146 +18731,384 @@
         <v>4</v>
       </c>
       <c r="D1078" s="3">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E1078" s="3">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1079" spans="1:5">
       <c r="A1079" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B1079" s="2">
         <v>2026</v>
       </c>
       <c r="C1079" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D1079" s="3">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="E1079" s="3">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1080" spans="1:5">
       <c r="A1080" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1080" s="2">
         <v>2026</v>
       </c>
       <c r="C1080" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1080" s="3">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E1080" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1081" spans="1:5">
       <c r="A1081" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1081" s="2">
         <v>2026</v>
       </c>
       <c r="C1081" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1081" s="3">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E1081" s="3">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1082" spans="1:5">
       <c r="A1082" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1082" s="2">
         <v>2026</v>
       </c>
       <c r="C1082" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1082" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E1082" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1083" spans="1:5">
       <c r="A1083" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B1083" s="2">
         <v>2026</v>
       </c>
       <c r="C1083" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D1083" s="3">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E1083" s="3">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1084" spans="1:5">
       <c r="A1084" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B1084" s="2">
         <v>2026</v>
       </c>
       <c r="C1084" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1084" s="3">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E1084" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1085" spans="1:5">
       <c r="A1085" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B1085" s="2">
         <v>2026</v>
       </c>
       <c r="C1085" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D1085" s="3">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="E1085" s="3">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1086" spans="1:5">
       <c r="A1086" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B1086" s="2">
         <v>2026</v>
       </c>
       <c r="C1086" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D1086" s="3">
+        <v>50</v>
+      </c>
+      <c r="E1086" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:5">
+      <c r="A1087" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1087" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1087" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1087" s="3">
+        <v>43</v>
+      </c>
+      <c r="E1087" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:5">
+      <c r="A1088" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1088" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1088" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1088" s="3">
+        <v>56</v>
+      </c>
+      <c r="E1088" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:5">
+      <c r="A1089" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1089" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1089" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1089" s="3">
+        <v>48</v>
+      </c>
+      <c r="E1089" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:5">
+      <c r="A1090" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1090" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1090" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1090" s="3">
+        <v>12</v>
+      </c>
+      <c r="E1090" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:5">
+      <c r="A1091" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1091" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1091" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1091" s="3">
+        <v>11</v>
+      </c>
+      <c r="E1091" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:5">
+      <c r="A1092" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1092" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1092" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1092" s="3">
+        <v>12</v>
+      </c>
+      <c r="E1092" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:5">
+      <c r="A1093" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1093" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1093" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1093" s="3">
+        <v>17</v>
+      </c>
+      <c r="E1093" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:5">
+      <c r="A1094" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1094" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1094" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1094" s="3">
+        <v>18</v>
+      </c>
+      <c r="E1094" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:5">
+      <c r="A1095" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1095" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1095" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1095" s="3">
+        <v>1</v>
+      </c>
+      <c r="E1095" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:5">
+      <c r="A1096" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1096" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1096" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1096" s="3">
+        <v>10</v>
+      </c>
+      <c r="E1096" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:5">
+      <c r="A1097" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1097" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1097" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1097" s="3">
+        <v>7</v>
+      </c>
+      <c r="E1097" s="3">
         <v>6</v>
       </c>
-      <c r="E1086" s="3">
+    </row>
+    <row r="1098" spans="1:5">
+      <c r="A1098" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1098" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1098" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1098" s="3">
+        <v>12</v>
+      </c>
+      <c r="E1098" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:5">
+      <c r="A1099" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1099" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1099" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1099" s="3">
         <v>6</v>
+      </c>
+      <c r="E1099" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:5">
+      <c r="A1100" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1100" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C1100" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1100" s="3">
+        <v>5</v>
+      </c>
+      <c r="E1100" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
